--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-30).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-30).xlsx
@@ -935,37 +935,37 @@
     <t>214</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>R$ 4.623,91</t>
-  </si>
-  <si>
-    <t>49.3</t>
-  </si>
-  <si>
-    <t>31.1</t>
-  </si>
-  <si>
-    <t>5.20</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 4.587,07</t>
+  </si>
+  <si>
+    <t>48.9</t>
+  </si>
+  <si>
+    <t>31.2</t>
+  </si>
+  <si>
+    <t>5.23</t>
   </si>
   <si>
     <t>19.8</t>
   </si>
   <si>
-    <t>7.7</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>37.9%</t>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>37.8%</t>
   </si>
   <si>
     <t>18.0%</t>
   </si>
   <si>
-    <t>2.6%</t>
+    <t>2.7%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -980,40 +980,40 @@
     <t>5.5%</t>
   </si>
   <si>
-    <t>3.0%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>1183.0</t>
-  </si>
-  <si>
-    <t>986.0</t>
-  </si>
-  <si>
-    <t>145.0</t>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>3.8%</t>
+  </si>
+  <si>
+    <t>1205.0</t>
+  </si>
+  <si>
+    <t>1005.0</t>
+  </si>
+  <si>
+    <t>148.0</t>
   </si>
   <si>
     <t>11.0</t>
   </si>
   <si>
-    <t>291.0</t>
-  </si>
-  <si>
-    <t>46.0</t>
+    <t>297.0</t>
+  </si>
+  <si>
+    <t>47.0</t>
   </si>
   <si>
     <t>12.0</t>
   </si>
   <si>
-    <t>301.0</t>
-  </si>
-  <si>
-    <t>162.0</t>
-  </si>
-  <si>
-    <t>212.0</t>
+    <t>309.0</t>
+  </si>
+  <si>
+    <t>164.0</t>
+  </si>
+  <si>
+    <t>214.0</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -6666,7 +6666,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6696,35 +6696,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>3796.6300000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>40</v>
+      </c>
+      <c r="O36" s="6">
+        <v>28</v>
+      </c>
+      <c r="P36" s="7">
+        <v>8.0012500000000006</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>29.900642307692308</v>
+      </c>
+      <c r="R36" s="8">
+        <v>18.210604545454547</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.17857142857142858</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7548,7 +7606,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7578,35 +7636,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>3830.4200000000001</v>
+      </c>
+      <c r="N42" s="6">
+        <v>43</v>
+      </c>
+      <c r="O42" s="6">
+        <v>27</v>
+      </c>
+      <c r="P42" s="7">
+        <v>5.0796756097560971</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>15.623455555555555</v>
+      </c>
+      <c r="R42" s="8">
+        <v>4.1253320000000002</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.40740740740740738</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -8897,7 +9013,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -8927,10 +9043,16 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>286.80000000000001</v>
+      </c>
+      <c r="N51" s="6">
+        <v>3</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
+      <c r="P51" s="7">
+        <v>4.6027833333333339</v>
+      </c>
       <c r="Q51" s="8"/>
       <c r="R51" s="8"/>
       <c r="S51" s="8"/>
@@ -9966,33 +10088,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>48</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -16454,7 +16622,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16484,14 +16652,26 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
+      <c r="M102" s="5">
+        <v>3615.6500000000001</v>
+      </c>
+      <c r="N102" s="6">
+        <v>30</v>
+      </c>
       <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
+      <c r="P102" s="7">
+        <v>7.5999999999999996</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>24.009999999999998</v>
+      </c>
+      <c r="R102" s="8">
+        <v>9.5666666666666664</v>
+      </c>
       <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
+      <c r="T102" s="9">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="U102" s="9"/>
       <c r="V102" s="9"/>
       <c r="W102" s="9"/>
@@ -30155,7 +30335,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30185,14 +30365,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>4884.4300000000003</v>
+      </c>
+      <c r="N195" s="6">
+        <v>55</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>5.1455134615384619</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>20.392028260869566</v>
+      </c>
+      <c r="R195" s="8">
+        <v>8.3365934782608697</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.21739130434782608</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>
